--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 00:15</t>
+          <t>2026-05-12 00:51</t>
         </is>
       </c>
     </row>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 00:51</t>
+          <t>2026-05-12 00:54</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>special church roof: low tile body, shallow low kubbe with 3 glazed marks; kubbe centered at (670342.95, 4539707.85) from Pervititch GeoTIFF kubbe mark; clocher 16.9 m from Pervititch raster clocher square within W-39/1</t>
+          <t>special church roof: low tile body, curved lead/zinc kubbe with 3 arched glazed eyes; kubbe centered at (670342.95, 4539707.85) from Pervititch GeoTIFF kubbe mark; clocher 16.9 m from Pervititch raster clocher square within W-39/1</t>
         </is>
       </c>
     </row>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 00:54</t>
+          <t>2026-05-12 01:22</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>ChurchBody, ChurchDome, Clocher, CorniceSurface, Door, GroundSurface, HeaderSurface, JambSurface, Mullion, PlinthSurface, RoofSurface, SillSurface, StringcourseSurface, Window</t>
+          <t>ChurchBody, ChurchDome, Clocher, CorniceSurface, GroundSurface, HeaderSurface, JambSurface, Mullion, PlinthSurface, RoofSurface, SillSurface, StringcourseSurface, Window</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 01:22</t>
+          <t>2026-05-12 01:54</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 01:54</t>
+          <t>2026-05-12 02:08</t>
         </is>
       </c>
     </row>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 02:08</t>
+          <t>2026-05-12 02:14</t>
         </is>
       </c>
     </row>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 02:14</t>
+          <t>2026-05-12 02:24</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>map+photo:cesme-left-side-adjacent-door: 1</t>
+          <t>map:pervititch:39-2-entrance-mounted-to-wall: 1</t>
         </is>
       </c>
     </row>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>map+photo:cesme-left-side-adjacent-door: 1</t>
+          <t>map:pervititch:39-2-entrance-mounted-to-wall: 1</t>
         </is>
       </c>
     </row>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 02:24</t>
+          <t>2026-05-12 02:31</t>
         </is>
       </c>
     </row>

--- a/output/block147_building_data.xlsx
+++ b/output/block147_building_data.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 02:31</t>
+          <t>2026-05-12 02:46</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="V34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" s="2" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="V37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" s="2" t="n">
         <v>0</v>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>Door, GroundSurface, MonumentBody, RoofSurface</t>
+          <t>GroundSurface, MonumentBody, RoofSurface</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>map:pervititch:39-2-entrance-mounted-to-wall: 1</t>
+          <t>non-building asset</t>
         </is>
       </c>
     </row>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>map:pervititch:39-2-entrance-mounted-to-wall: 1</t>
+          <t>non-building asset</t>
         </is>
       </c>
     </row>
